--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Александр\YandexDisk\Типо педагог\OurLib\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ON_WORK\GitBin\Библиотеки компонентов\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C470B04-F5D5-43A4-AB2C-6109D1E3026D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1120797-E6A0-4E02-9942-D9B5C28ED5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="961" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="961" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -18,22 +18,23 @@
     <sheet name="04 - Датчики" sheetId="2" r:id="rId3"/>
     <sheet name="05 - Питание" sheetId="17" r:id="rId4"/>
     <sheet name="06 - Микроконтроллеры" sheetId="4" r:id="rId5"/>
-    <sheet name="07 - Интерфейсы" sheetId="21" r:id="rId6"/>
-    <sheet name="08 - Кварцы" sheetId="10" r:id="rId7"/>
-    <sheet name="09 - Диоды" sheetId="11" r:id="rId8"/>
-    <sheet name="10 - Транзисторы" sheetId="12" r:id="rId9"/>
-    <sheet name="11 - Разъемы" sheetId="14" r:id="rId10"/>
-    <sheet name="12 - Антенны" sheetId="16" r:id="rId11"/>
-    <sheet name="13 - Кнопки" sheetId="18" r:id="rId12"/>
-    <sheet name="14 - Моторы" sheetId="19" r:id="rId13"/>
-    <sheet name="15 - Светодиоды" sheetId="20" r:id="rId14"/>
+    <sheet name="07 - Логика" sheetId="22" r:id="rId6"/>
+    <sheet name="08 - Интерфейсы" sheetId="21" r:id="rId7"/>
+    <sheet name="09 - Кварцы" sheetId="10" r:id="rId8"/>
+    <sheet name="10 - Диоды" sheetId="11" r:id="rId9"/>
+    <sheet name="11 - Транзисторы" sheetId="12" r:id="rId10"/>
+    <sheet name="12 - Разъемы" sheetId="14" r:id="rId11"/>
+    <sheet name="13 - Антенны" sheetId="16" r:id="rId12"/>
+    <sheet name="14 - Кнопки" sheetId="18" r:id="rId13"/>
+    <sheet name="15 - Моторы" sheetId="19" r:id="rId14"/>
+    <sheet name="16 - Светодиоды" sheetId="20" r:id="rId15"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="171">
   <si>
     <t>Part Number</t>
   </si>
@@ -528,6 +529,24 @@
   </si>
   <si>
     <t>CSMD_7343_P</t>
+  </si>
+  <si>
+    <t>NE555</t>
+  </si>
+  <si>
+    <t>Счетчик</t>
+  </si>
+  <si>
+    <t>555 таймер - счетчик</t>
+  </si>
+  <si>
+    <t>DIP-8</t>
+  </si>
+  <si>
+    <t>Ics - Logic.SchLib</t>
+  </si>
+  <si>
+    <t>Pacages DIP.PcbLib</t>
   </si>
 </sst>
 </file>
@@ -859,23 +878,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="29.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -919,7 +938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -952,26 +971,23 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" customWidth="1"/>
+    <col min="11" max="11" width="29.5546875" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1015,340 +1031,84 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>137</v>
+        <v>68</v>
       </c>
       <c r="J2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="J3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="K4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="K5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" t="s">
-        <v>120</v>
-      </c>
-      <c r="J6" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" t="s">
-        <v>122</v>
-      </c>
-      <c r="J8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J10" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J11" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J14" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
-      <c r="K15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J16" t="s">
-        <v>65</v>
-      </c>
-      <c r="K16" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1358,24 +1118,26 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
-    <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1419,67 +1181,367 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>137</v>
+      </c>
+      <c r="E2" t="s">
+        <v>137</v>
       </c>
       <c r="J2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="K2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>85</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J4" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="s">
+        <v>122</v>
+      </c>
+      <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J15" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1523,24 +1585,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="J2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K2" t="s">
-        <v>135</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1549,20 +1628,24 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1606,24 +1689,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J2" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1632,24 +1715,107 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" customWidth="1"/>
-    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" customWidth="1"/>
+    <col min="11" max="11" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1693,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>131</v>
       </c>
@@ -1721,23 +1887,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.85546875" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="35.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1807,7 +1973,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>160</v>
       </c>
@@ -1844,22 +2010,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1903,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1926,7 +2092,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -1946,7 +2112,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1977,18 +2143,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2032,7 +2198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -2055,7 +2221,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -2078,7 +2244,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>156</v>
       </c>
@@ -2109,22 +2275,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2168,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2188,7 +2354,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2208,7 +2374,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2228,7 +2394,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2254,20 +2420,25 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCFE1EE-90EE-45BF-9CB2-8076B36A7F6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D731ECE-5AA0-42F0-8161-7F6057C710A8}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2311,27 +2482,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="J2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2340,23 +2511,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCFE1EE-90EE-45BF-9CB2-8076B36A7F6D}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.140625" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2400,24 +2568,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>152</v>
+      </c>
+      <c r="C2" t="s">
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="K2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2426,22 +2597,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2485,96 +2657,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G2" t="s">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
-    <col min="11" max="11" width="29.5703125" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2618,83 +2742,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>141</v>
+      </c>
+      <c r="F2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
+        <v>143</v>
       </c>
       <c r="J2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K2" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="J3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
       <c r="J4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="K4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K5" t="s">
         <v>145</v>
       </c>
     </row>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ON_WORK\GitBin\Библиотеки компонентов\my-altium-library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_OnWork\01_GITLAB_REPOS\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1120797-E6A0-4E02-9942-D9B5C28ED5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE729590-56A4-49A1-89CF-0FE59AC0F3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="961" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="961" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -543,10 +543,10 @@
     <t>DIP-8</t>
   </si>
   <si>
-    <t>Ics - Logic.SchLib</t>
-  </si>
-  <si>
-    <t>Pacages DIP.PcbLib</t>
+    <t>DIP.PcbLib</t>
+  </si>
+  <si>
+    <t>ICs - Logic.SchLib</t>
   </si>
 </sst>
 </file>
@@ -878,23 +878,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" customWidth="1"/>
-    <col min="11" max="11" width="29.88671875" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -973,21 +973,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" customWidth="1"/>
-    <col min="11" max="11" width="29.5546875" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="11" max="11" width="29.5703125" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1120,24 +1120,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>91</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>93</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>94</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>95</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -1448,7 +1448,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>99</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -1526,22 +1526,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.44140625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1630,22 +1630,22 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -1717,18 +1717,18 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="27.88671875" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>125</v>
       </c>
@@ -1800,22 +1800,22 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" customWidth="1"/>
-    <col min="11" max="11" width="28.5546875" customWidth="1"/>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>131</v>
       </c>
@@ -1887,23 +1887,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
-    <col min="11" max="11" width="35.88671875" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
+    <col min="11" max="11" width="35.85546875" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>160</v>
       </c>
@@ -2010,22 +2010,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -2143,18 +2143,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>79</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>156</v>
       </c>
@@ -2275,22 +2275,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="26.6640625" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -2422,23 +2422,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D731ECE-5AA0-42F0-8161-7F6057C710A8}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="14.77734375" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>165</v>
       </c>
@@ -2499,10 +2499,10 @@
         <v>168</v>
       </c>
       <c r="J2" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" t="s">
         <v>169</v>
-      </c>
-      <c r="K2" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2513,18 +2513,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DCFE1EE-90EE-45BF-9CB2-8076B36A7F6D}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="29.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.6640625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -2599,21 +2599,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.140625" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -2685,20 +2685,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>47</v>
       </c>

--- a/OurLib.xlsx
+++ b/OurLib.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00_OnWork\01_GITLAB_REPOS\my-altium-library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ON_WORK\GitBin\Components Libs\my-altium-library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4760343-4C86-4F6C-9DDE-58248BB6E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BAEF18-82F9-4FB6-84D4-7484C701BA47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01 - Резисторы" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="183">
   <si>
     <t>Part Number</t>
   </si>
@@ -567,16 +567,43 @@
   </si>
   <si>
     <t>LEDs.PcbLib</t>
+  </si>
+  <si>
+    <t>74HC00D</t>
+  </si>
+  <si>
+    <t>5 Х 2И-НЕ</t>
+  </si>
+  <si>
+    <t>SO-14</t>
+  </si>
+  <si>
+    <t>SO-Packages.PcbLib</t>
+  </si>
+  <si>
+    <t>QFN.PcbLib</t>
+  </si>
+  <si>
+    <t>SOD.PcbLib</t>
+  </si>
+  <si>
+    <t>SOT.PcbLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -805,23 +832,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="29.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -865,7 +892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -900,21 +927,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
-    <col min="11" max="11" width="29.5703125" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" customWidth="1"/>
+    <col min="11" max="11" width="29.5546875" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -958,7 +985,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -975,10 +1002,10 @@
         <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -995,10 +1022,10 @@
         <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -1015,10 +1042,10 @@
         <v>102</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>107</v>
       </c>
@@ -1035,7 +1062,7 @@
         <v>102</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1047,24 +1074,24 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:N16"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>109</v>
       </c>
@@ -1128,7 +1155,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>113</v>
       </c>
@@ -1148,7 +1175,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>114</v>
       </c>
@@ -1168,7 +1195,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -1191,7 +1218,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>120</v>
       </c>
@@ -1214,7 +1241,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -1237,7 +1264,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>126</v>
       </c>
@@ -1260,7 +1287,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>129</v>
       </c>
@@ -1283,7 +1310,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>132</v>
       </c>
@@ -1306,7 +1333,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>135</v>
       </c>
@@ -1329,7 +1356,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>138</v>
       </c>
@@ -1352,7 +1379,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>141</v>
       </c>
@@ -1375,7 +1402,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>144</v>
       </c>
@@ -1398,7 +1425,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>147</v>
       </c>
@@ -1421,7 +1448,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>150</v>
       </c>
@@ -1453,22 +1480,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="9" max="9" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -1529,7 +1556,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -1558,22 +1585,22 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1617,7 +1644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>159</v>
       </c>
@@ -1646,18 +1673,18 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1728,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>164</v>
       </c>
@@ -1730,22 +1757,22 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" customWidth="1"/>
-    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.44140625" customWidth="1"/>
+    <col min="11" max="11" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1789,7 +1816,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>170</v>
       </c>
@@ -1818,23 +1845,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.85546875" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="11" width="35.88671875" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1878,7 +1905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1904,7 +1931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1942,22 +1969,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2001,7 +2028,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -2021,10 +2048,10 @@
         <v>39</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>41</v>
       </c>
@@ -2040,11 +2067,8 @@
       <c r="J3" t="s">
         <v>39</v>
       </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -2064,7 +2088,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2076,18 +2100,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="41.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="30.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2131,7 +2155,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -2151,10 +2175,10 @@
         <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -2174,10 +2198,10 @@
         <v>50</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -2197,7 +2221,7 @@
         <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2209,22 +2233,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2292,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -2288,7 +2312,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -2305,10 +2329,10 @@
         <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -2328,7 +2352,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -2356,24 +2380,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.5703125" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="18.5546875" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2417,7 +2441,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -2440,7 +2464,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -2463,27 +2487,51 @@
         <v>72</v>
       </c>
     </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J4" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" t="s">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" customWidth="1"/>
+    <col min="11" max="11" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2527,7 +2575,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
@@ -2547,7 +2595,7 @@
         <v>82</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2559,21 +2607,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="30.140625" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" customWidth="1"/>
+    <col min="11" max="11" width="30.109375" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2617,7 +2665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>83</v>
       </c>
@@ -2646,20 +2694,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="6" max="9" width="13.28515625" customWidth="1"/>
+    <col min="1" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.88671875" customWidth="1"/>
+    <col min="5" max="5" width="16.88671875" customWidth="1"/>
+    <col min="6" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="14" width="5.28515625" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" customWidth="1"/>
+    <col min="13" max="14" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2703,7 +2751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>88</v>
       </c>
@@ -2726,10 +2774,10 @@
         <v>93</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -2742,14 +2790,20 @@
       <c r="E3" t="s">
         <v>90</v>
       </c>
+      <c r="F3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
       <c r="J3" t="s">
         <v>93</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2762,11 +2816,17 @@
       <c r="E4" t="s">
         <v>90</v>
       </c>
+      <c r="F4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" t="s">
+        <v>92</v>
+      </c>
       <c r="J4" t="s">
         <v>93</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
